--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486837_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486837_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6427</v>
+        <v>4.6444</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9902</v>
+        <v>4.4389</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6525</v>
+        <v>0.2055</v>
       </c>
       <c r="G2" t="n">
         <v>1.4466</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1221</v>
+        <v>1.1238</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0884</v>
+        <v>1.5371</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0337</v>
+        <v>-0.4133</v>
       </c>
       <c r="V2" t="n">
         <v>-0.243</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2341</v>
+        <v>4.216</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0992</v>
+        <v>3.9817</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1349</v>
+        <v>0.2342</v>
       </c>
       <c r="G3" t="n">
         <v>-1.4956</v>
@@ -688,13 +688,13 @@
         <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7337</v>
+        <v>0.2481</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0546</v>
+        <v>0.9371</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7883</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>3.7257</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6191</v>
+        <v>1.9006</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6238</v>
+        <v>-0.045</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9953</v>
+        <v>1.9456</v>
       </c>
       <c r="G4" t="n">
         <v>2.7128</v>
@@ -766,13 +766,13 @@
         <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3736</v>
+        <v>0.6552</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5719</v>
+        <v>0.9031</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1983</v>
+        <v>-0.248</v>
       </c>
       <c r="V4" t="n">
         <v>0.6565</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2454</v>
+        <v>1.3943</v>
       </c>
       <c r="E5" t="n">
         <v>1.9429</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6975</v>
+        <v>-0.5485</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4471</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3421</v>
+        <v>-0.1931</v>
       </c>
       <c r="T5" t="n">
         <v>0.0548</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.397</v>
+        <v>-0.248</v>
       </c>
       <c r="V5" t="n">
         <v>2.4554</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. SECK DIOP</t>
+          <t>A. ROMERO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6538</v>
+        <v>-1.0177</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5006</v>
+        <v>0.3164</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1545</v>
+        <v>-1.3341</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.0853</v>
+        <v>-0.9458</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1787</v>
+        <v>-0.4484</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9066</v>
+        <v>-0.4974</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6011</v>
+        <v>0.1442</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0744</v>
+        <v>0.1035</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4841</v>
+        <v>-1.0899</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1043</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3799</v>
+        <v>-0.5381</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3169</v>
+        <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7943</v>
+        <v>0.0206</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2682</v>
+        <v>0.1723</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.474</v>
+        <v>-0.1516</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7989</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5133</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3715</v>
+        <v>-1.1109</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4417</v>
+        <v>-0.1314</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9795</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3936</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.171</v>
+        <v>0.0896</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.138</v>
+        <v>0.1723</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.033</v>
+        <v>-0.0827</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ROMERO GARCIA</t>
+          <t>K. SECK DIOP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4025</v>
+        <v>-1.1654</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0061</v>
+        <v>0.0387</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4086</v>
+        <v>-1.2041</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9458</v>
+        <v>-3.0853</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4484</v>
+        <v>-2.1787</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4974</v>
+        <v>-0.9066</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1442</v>
+        <v>-1.6011</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1035</v>
+        <v>-1.0744</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0407</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0899</v>
+        <v>-1.4841</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-1.1043</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5381</v>
+        <v>-0.3799</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1931</v>
+        <v>2.3169</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3641</v>
+        <v>0.2827</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.138</v>
+        <v>0.8063</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2261</v>
+        <v>-0.5236</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>0.2856</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.7989</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5822</v>
+        <v>-1.243</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7939</v>
+        <v>-2.3802</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2117</v>
+        <v>1.1372</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6634</v>
@@ -1156,13 +1156,13 @@
         <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3088</v>
+        <v>0.648</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4962</v>
+        <v>0.9099</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1873</v>
+        <v>-0.2618</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.692</v>
+        <v>-1.5871</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1593</v>
+        <v>-0.1042</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5326</v>
+        <v>-1.483</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5044</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1876</v>
+        <v>-0.0828</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2207</v>
+        <v>-0.1655</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0448</v>
+        <v>-3.7608</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7386</v>
+        <v>-1.7526</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3062</v>
+        <v>-2.0082</v>
       </c>
       <c r="G11" t="n">
         <v>0.5145999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1805</v>
+        <v>0.1034</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2486</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9319</v>
+        <v>-0.6339</v>
       </c>
       <c r="V11" t="n">
         <v>-2.255</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.994499999999999</v>
+        <v>2.2704</v>
       </c>
       <c r="E12" t="n">
-        <v>6.029299999999999</v>
+        <v>6.3052</v>
       </c>
       <c r="F12" t="n">
         <v>-4.0349</v>
@@ -1369,7 +1369,7 @@
         <v>6.558399999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.237499999999999</v>
+        <v>-2.2375</v>
       </c>
       <c r="M12" t="n">
         <v>-12.1815</v>
@@ -1390,10 +1390,10 @@
         <v>13.5154</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6198</v>
+        <v>2.8955</v>
       </c>
       <c r="T12" t="n">
-        <v>5.788800000000001</v>
+        <v>6.064800000000001</v>
       </c>
       <c r="U12" t="n">
         <v>-3.1691</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SOLE MOURATAY</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2365</v>
+        <v>4.3676</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2668</v>
+        <v>3.3551</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0302</v>
+        <v>1.0126</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0587</v>
+        <v>2.3578</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6895</v>
+        <v>-0.9383</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6308</v>
+        <v>3.2961</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4257</v>
+        <v>2.8903</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2772</v>
+        <v>0.442</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1485</v>
+        <v>2.4484</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4844</v>
+        <v>-0.5325</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9667</v>
+        <v>-1.3802</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5178</v>
+        <v>0.8477</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
         <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>1.732</v>
+        <v>-0.4689</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5368</v>
+        <v>-0.0832</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8048</v>
+        <v>-0.3857</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7563</v>
+        <v>1.5133</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4281</v>
+        <v>1.5133</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>M. SOLE MOURATAY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.088</v>
+        <v>2.0492</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5277</v>
+        <v>1.7154</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5603</v>
+        <v>0.3338</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3578</v>
+        <v>-0.0587</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9383</v>
+        <v>-0.6895</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2961</v>
+        <v>0.6308</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8903</v>
+        <v>1.4257</v>
       </c>
       <c r="K14" t="n">
-        <v>0.442</v>
+        <v>0.2772</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4484</v>
+        <v>1.1485</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5325</v>
+        <v>-1.4844</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3802</v>
+        <v>-0.9667</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8477</v>
+        <v>-0.5178</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="R14" t="n">
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7485</v>
+        <v>0.5447</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9106</v>
+        <v>0.9855</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8379</v>
+        <v>-0.4408</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5133</v>
+        <v>1.7563</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5133</v>
+        <v>1.4281</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PEREZ RUIZ</t>
+          <t>J. ONGIL FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7575</v>
+        <v>0.9276</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08749999999999999</v>
+        <v>1.8902</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6699000000000001</v>
+        <v>-0.9626</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0181</v>
+        <v>3.5993</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7934</v>
+        <v>0.5927</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8116</v>
+        <v>3.0066</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4639</v>
+        <v>4.0557</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1035</v>
+        <v>0.8004</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5674</v>
+        <v>3.2554</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4821</v>
+        <v>-0.4564</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8969</v>
+        <v>-0.2077</v>
       </c>
       <c r="O15" t="n">
-        <v>1.379</v>
+        <v>-0.2487</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.033</v>
+        <v>0.0001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5515</v>
+        <v>-0.0417</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5845</v>
+        <v>0.0417</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>R. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3605</v>
+        <v>0.9146</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7464</v>
+        <v>-0.1193</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1069</v>
+        <v>1.034</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2597</v>
+        <v>0.0181</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4413</v>
+        <v>-0.7934</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8183</v>
+        <v>0.8116</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4604</v>
+        <v>-0.4639</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3384</v>
+        <v>0.1035</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1221</v>
+        <v>-0.5674</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2008</v>
+        <v>0.4821</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.897</v>
+        <v>-0.8969</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6962</v>
+        <v>1.379</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.3169</v>
+        <v>0.7723</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1048</v>
+        <v>0.1242</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6894</v>
+        <v>0.3446</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5845</v>
+        <v>-0.2204</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3129</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.3129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ONGIL FERNANDEZ</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2693</v>
+        <v>0.4695</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2697</v>
+        <v>-0.8498</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.539</v>
+        <v>1.3193</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5993</v>
+        <v>1.2597</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5927</v>
+        <v>0.4413</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0066</v>
+        <v>0.8183</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0557</v>
+        <v>1.4604</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8004</v>
+        <v>1.3384</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2554</v>
+        <v>0.1221</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4564</v>
+        <v>-0.2008</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2077</v>
+        <v>-0.897</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2487</v>
+        <v>0.6962</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1585</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1239</v>
+        <v>-2.8962</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1969</v>
+        <v>0.2138</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6622</v>
+        <v>0.5859</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5347</v>
+        <v>-0.3721</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5133</v>
+        <v>1.3129</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5133</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6019</v>
+        <v>-2.1441</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1886</v>
+        <v>-1.9817</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4133</v>
+        <v>-0.1623</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3895</v>
@@ -1858,13 +1858,13 @@
         <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3475</v>
+        <v>0.1103</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3031</v>
+        <v>0.5099</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6506</v>
+        <v>-0.3997</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6086</v>
+        <v>-2.5081</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3628</v>
+        <v>-0.4662</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2458</v>
+        <v>-2.0418</v>
       </c>
       <c r="G19" t="n">
         <v>-0.083</v>
@@ -1936,13 +1936,13 @@
         <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4857</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6615</v>
+        <v>0.5581</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1758</v>
+        <v>0.0282</v>
       </c>
       <c r="V19" t="n">
         <v>-3.3975</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9571</v>
+        <v>-2.6234</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1811</v>
+        <v>0.4913</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.1381</v>
+        <v>-3.1147</v>
       </c>
       <c r="G20" t="n">
         <v>2.1573</v>
@@ -2014,13 +2014,13 @@
         <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6164</v>
+        <v>-0.2827</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0004</v>
+        <v>0.3099</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.616</v>
+        <v>-0.5926</v>
       </c>
       <c r="V20" t="n">
         <v>-3.7257</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.994399999999999</v>
+        <v>1.4529</v>
       </c>
       <c r="E21" t="n">
-        <v>4.034999999999999</v>
+        <v>4.035</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.029299999999999</v>
+        <v>-2.581699999999999</v>
       </c>
       <c r="G21" t="n">
         <v>7.861000000000001</v>
@@ -2062,7 +2062,7 @@
         <v>1.7233</v>
       </c>
       <c r="I21" t="n">
-        <v>6.137700000000001</v>
+        <v>6.1377</v>
       </c>
       <c r="J21" t="n">
         <v>12.1815</v>
@@ -2074,7 +2074,7 @@
         <v>3.9001</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.3205</v>
+        <v>-4.320499999999999</v>
       </c>
       <c r="N21" t="n">
         <v>-6.558300000000001</v>
@@ -2092,13 +2092,13 @@
         <v>10.6192</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6198</v>
+        <v>0.8277000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1691</v>
+        <v>3.169</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.7888</v>
+        <v>-2.3414</v>
       </c>
       <c r="V21" t="n">
         <v>-4.339600000000001</v>
